--- a/data-raw/ficha_tecnica.xlsx
+++ b/data-raw/ficha_tecnica.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29212"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m753205\Desktop\99 TABELAS APOIO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x1569275\CAMG\Splor Geral - @dcppn\00- DCPPN 2027\PPAG e LOA 2027\Dados para Volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_F2517A56A4FE8C51D13D146938BF790038D4D514" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>servidor</t>
   </si>
@@ -50,18 +49,12 @@
     <t>ordem</t>
   </si>
   <si>
-    <t>Romeu Zema Neto</t>
-  </si>
-  <si>
     <t>Governador do Estado de Minas Gerais</t>
   </si>
   <si>
     <t>Mateus Simões de Almeida</t>
   </si>
   <si>
-    <t>Vice-Governador do Estado de Minas Gerais</t>
-  </si>
-  <si>
     <t>Silvia Caroline Listgarten Dias</t>
   </si>
   <si>
@@ -113,8 +106,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -367,16 +360,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.25" customWidth="1"/>
     <col min="2" max="2" width="67" customWidth="1"/>
     <col min="3" max="3" width="7.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -387,18 +380,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -409,7 +402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -420,7 +413,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -431,8 +424,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -442,8 +435,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -453,7 +446,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -464,7 +457,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -475,7 +468,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -484,17 +477,6 @@
       </c>
       <c r="C10" s="1">
         <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="1">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -504,8 +486,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7797dc5feb179b4da55a9ebddd321181">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90078f443198b6d5c0fd169535a443b9" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="b1e0f6055e0e9a4b9e75d6c71ee7de91">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b43930f3490e4d4da1ab3f8da7df6f51" ns2:_="" ns3:_="">
     <xsd:import namespace="6f4338ef-addb-4c87-aefe-1895241b335f"/>
     <xsd:import namespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
     <xsd:element name="properties">
@@ -764,34 +766,46 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDE799C8-D304-41C1-9B65-F57F9E44773C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7942961-9DCC-406C-B52B-375FF7069311}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B4A3115-33B5-4A64-9E7B-CE2DE6037C3F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B4A3115-33B5-4A64-9E7B-CE2DE6037C3F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7942961-9DCC-406C-B52B-375FF7069311}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1B3D0F0-1096-4835-91EC-3235D6F9F96F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data-raw/ficha_tecnica.xlsx
+++ b/data-raw/ficha_tecnica.xlsx
@@ -486,26 +486,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="b1e0f6055e0e9a4b9e75d6c71ee7de91">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b43930f3490e4d4da1ab3f8da7df6f51" ns2:_="" ns3:_="">
     <xsd:import namespace="6f4338ef-addb-4c87-aefe-1895241b335f"/>
@@ -766,32 +746,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7942961-9DCC-406C-B52B-375FF7069311}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B4A3115-33B5-4A64-9E7B-CE2DE6037C3F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1B3D0F0-1096-4835-91EC-3235D6F9F96F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -808,4 +783,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B4A3115-33B5-4A64-9E7B-CE2DE6037C3F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7942961-9DCC-406C-B52B-375FF7069311}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>